--- a/src/cubes/data/materials/windows.xlsx
+++ b/src/cubes/data/materials/windows.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/materials/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hannes/Work/elizabeth-homes/src/cubes/data/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317513D9-E3C7-4A44-A848-7A09DAFCD4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDF4B3C-5750-4045-9FC3-B169DCBF4D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{47704123-5C42-9841-98FC-8623E63A368D}"/>
+    <workbookView xWindow="-4920" yWindow="-21760" windowWidth="25200" windowHeight="18380" xr2:uid="{47704123-5C42-9841-98FC-8623E63A368D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -105,6 +105,18 @@
   </si>
   <si>
     <t>Solar Heat Gain Coefficient</t>
+  </si>
+  <si>
+    <t>Clear_6mm_CODE</t>
+  </si>
+  <si>
+    <t>LoE_clear_3mm_CODE</t>
+  </si>
+  <si>
+    <t>LoE_clear_3mm_rev_CODE</t>
+  </si>
+  <si>
+    <t>Clear_3mm_CODE</t>
   </si>
 </sst>
 </file>
@@ -148,10 +160,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,10 +477,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21125F1D-BB2D-604B-8747-268ACA9BD3EF}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -565,7 +578,7 @@
       <c r="N2">
         <v>0.9</v>
       </c>
-      <c r="Q2" s="2" t="b">
+      <c r="Q2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -609,7 +622,7 @@
       <c r="N3">
         <v>0.9</v>
       </c>
-      <c r="Q3" s="2" t="b">
+      <c r="Q3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -626,7 +639,7 @@
       <c r="P4">
         <v>0.35</v>
       </c>
-      <c r="Q4" s="2" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -643,7 +656,7 @@
       <c r="P5">
         <v>0.86</v>
       </c>
-      <c r="Q5" s="2" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -660,8 +673,184 @@
       <c r="P6">
         <v>0.8</v>
       </c>
-      <c r="Q6" s="2" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="E7">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="F7">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="G7">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="H7">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="I7">
+        <v>0.08</v>
+      </c>
+      <c r="J7">
+        <v>0.08</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0.84</v>
+      </c>
+      <c r="M7">
+        <v>0.84</v>
+      </c>
+      <c r="N7">
+        <v>0.9</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E8">
+        <v>0.63</v>
+      </c>
+      <c r="F8">
+        <v>0.19</v>
+      </c>
+      <c r="G8">
+        <v>0.22</v>
+      </c>
+      <c r="H8">
+        <v>0.85</v>
+      </c>
+      <c r="I8">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J8">
+        <v>0.79</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0.84</v>
+      </c>
+      <c r="M8">
+        <v>0.1</v>
+      </c>
+      <c r="N8">
+        <v>0.9</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E9">
+        <v>0.63</v>
+      </c>
+      <c r="F9">
+        <v>0.19</v>
+      </c>
+      <c r="G9">
+        <v>0.22</v>
+      </c>
+      <c r="H9">
+        <v>0.85</v>
+      </c>
+      <c r="I9">
+        <v>0.79</v>
+      </c>
+      <c r="J9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0.1</v>
+      </c>
+      <c r="M9">
+        <v>0.84</v>
+      </c>
+      <c r="N9">
+        <v>0.9</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E10">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="F10">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G10">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="H10">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="I10">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="J10">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0.84</v>
+      </c>
+      <c r="M10">
+        <v>0.84</v>
+      </c>
+      <c r="N10">
+        <v>0.9</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
